--- a/九龙-将军澳-Seasons Place/Seasons Place_销控明细表.xlsx
+++ b/九龙-将军澳-Seasons Place/Seasons Place_销控明细表.xlsx
@@ -759,7 +759,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -22491,7 +22491,7 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -22693,7 +22693,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -41252,20 +41252,20 @@
 (24年-04月-18日)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>C | 453呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -41284,12 +41284,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -44537,20 +44537,20 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>C | 337呎 (1房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 441呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -44561,12 +44561,12 @@
 (26年-05月-17日)</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>F | 447呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
